--- a/docs/boxplots_dna-rna_amp3020.xlsx
+++ b/docs/boxplots_dna-rna_amp3020.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luigui/Documents/amps_microbiome_2025/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F741494-434E-2B48-8130-ADF210AECCAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF2B915E-5365-1145-B62F-D8FC13CF1936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{4D42E9DE-6820-2440-BB8C-1FD8983C094A}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" activeTab="3" xr2:uid="{4D42E9DE-6820-2440-BB8C-1FD8983C094A}"/>
   </bookViews>
   <sheets>
-    <sheet name="dna_amp3020" sheetId="1" r:id="rId1"/>
-    <sheet name="rna_amp3020" sheetId="2" r:id="rId2"/>
+    <sheet name="dna_amp3020_fago" sheetId="1" r:id="rId1"/>
+    <sheet name="rna_amp3020_fago" sheetId="2" r:id="rId2"/>
+    <sheet name="dna_amp3020_bacteria" sheetId="3" r:id="rId3"/>
+    <sheet name="rna_amp3020_bacteria" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="86">
   <si>
     <t>sample</t>
   </si>
@@ -160,18 +162,160 @@
   </si>
   <si>
     <t>OMC-258</t>
+  </si>
+  <si>
+    <t>015_B4_ribopicker_nonrrna_paired_R1_kneaddata_R1.fq.gz</t>
+  </si>
+  <si>
+    <t>024_B2_ribopicker_nonrrna_paired_R1_kneaddata_R1.fq.gz</t>
+  </si>
+  <si>
+    <t>074_B2_ribopicker_nonrrna_paired_R1_kneaddata_R1.fq.gz</t>
+  </si>
+  <si>
+    <t>090_subseq_ribopicker_nonrrna_paired_R1_kneaddata_R1.fq.gz</t>
+  </si>
+  <si>
+    <t>146_B1_ribopicker_nonrrna_paired_R1_kneaddata_R1.fq.gz</t>
+  </si>
+  <si>
+    <t>153_B3_ribopicker_nonrrna_paired_R1_kneaddata_R1.fq.gz</t>
+  </si>
+  <si>
+    <t>164_B1_ribopicker_nonrrna_paired_R1_kneaddata_R1.fq.gz</t>
+  </si>
+  <si>
+    <t>258_B3_ribopicker_nonrrna_paired_R1_kneaddata_R1.fq.gz</t>
+  </si>
+  <si>
+    <t>Final-All_ViralReads_H-10_R1.fq.gz</t>
+  </si>
+  <si>
+    <t>Final-All_ViralReads_H-118_R1.fq.gz</t>
+  </si>
+  <si>
+    <t>Final-All_ViralReads_H-119_R1.fq.gz</t>
+  </si>
+  <si>
+    <t>Final-All_ViralReads_H-120_R1.fq.gz</t>
+  </si>
+  <si>
+    <t>Final-All_ViralReads_H-124_R1.fq.gz</t>
+  </si>
+  <si>
+    <t>Final-All_ViralReads_H-147_R1.fq.gz</t>
+  </si>
+  <si>
+    <t>Final-All_ViralReads_H-161_R1.fq.gz</t>
+  </si>
+  <si>
+    <t>Final-All_ViralReads_H-169_R1.fq.gz</t>
+  </si>
+  <si>
+    <t>Final-All_ViralReads_H-193_R1.fq.gz</t>
+  </si>
+  <si>
+    <t>Final-All_ViralReads_H-314_R1.fq.gz</t>
+  </si>
+  <si>
+    <t>Final-All_ViralReads_O-121_R1.fq.gz</t>
+  </si>
+  <si>
+    <t>Final-All_ViralReads_O-122_R1.fq.gz</t>
+  </si>
+  <si>
+    <t>Final-All_ViralReads_O-123_R1.fq.gz</t>
+  </si>
+  <si>
+    <t>Final-All_ViralReads_O-152_R1.fq.gz</t>
+  </si>
+  <si>
+    <t>Final-All_ViralReads_O-39_R1.fq.gz</t>
+  </si>
+  <si>
+    <t>Final-All_ViralReads_O-418_R1.fq.gz</t>
+  </si>
+  <si>
+    <t>Final-All_ViralReads_O-420_R1.fq.gz</t>
+  </si>
+  <si>
+    <t>Final-All_ViralReads_O-434_R1.fq.gz</t>
+  </si>
+  <si>
+    <t>Final-All_ViralReads_O-445_R1.fq.gz</t>
+  </si>
+  <si>
+    <t>Final-All_ViralReads_O-90_R1.fq.gz</t>
+  </si>
+  <si>
+    <t>Final-All_ViralReads_OMC-124_R1.fq.gz</t>
+  </si>
+  <si>
+    <t>Final-All_ViralReads_OMC-125_R1.fq.gz</t>
+  </si>
+  <si>
+    <t>Final-All_ViralReads_OMC-126_R1.fq.gz</t>
+  </si>
+  <si>
+    <t>Final-All_ViralReads_OMC-288_R1.fq.gz</t>
+  </si>
+  <si>
+    <t>Final-All_ViralReads_OMC-446_R1.fq.gz</t>
+  </si>
+  <si>
+    <t>Final-All_ViralReads_OMC-55_R1.fq.gz</t>
+  </si>
+  <si>
+    <t>Final-All_ViralReads_OMC-64_R1.fq.gz</t>
+  </si>
+  <si>
+    <t>Final-All_ViralReads_OMC-87_R1.fq.gz</t>
+  </si>
+  <si>
+    <t>viral_allsamples_R1.fq.gz</t>
+  </si>
+  <si>
+    <t>015_B4</t>
+  </si>
+  <si>
+    <t>024_B2</t>
+  </si>
+  <si>
+    <t>074_B2</t>
+  </si>
+  <si>
+    <t>090_subseq</t>
+  </si>
+  <si>
+    <t>146_B1</t>
+  </si>
+  <si>
+    <t>153_B3</t>
+  </si>
+  <si>
+    <t>164_B1</t>
+  </si>
+  <si>
+    <t>258_B3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -195,9 +339,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -226,7 +371,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>126999</xdr:colOff>
+      <xdr:colOff>126998</xdr:colOff>
       <xdr:row>87</xdr:row>
       <xdr:rowOff>148167</xdr:rowOff>
     </xdr:to>
@@ -270,7 +415,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>143934</xdr:colOff>
+      <xdr:colOff>143933</xdr:colOff>
       <xdr:row>65</xdr:row>
       <xdr:rowOff>110067</xdr:rowOff>
     </xdr:to>
@@ -314,7 +459,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
+      <xdr:colOff>76199</xdr:colOff>
       <xdr:row>43</xdr:row>
       <xdr:rowOff>143933</xdr:rowOff>
     </xdr:to>
@@ -358,7 +503,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>152401</xdr:colOff>
+      <xdr:colOff>152400</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
@@ -385,6 +530,202 @@
         <a:xfrm>
           <a:off x="5067301" y="0"/>
           <a:ext cx="5871633" cy="4381500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>65615</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>33867</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>99481</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>148167</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23E73FB9-266A-7949-9ADC-80572AF64328}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId6"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19284948" y="13445067"/>
+          <a:ext cx="5842000" cy="4381500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>82550</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>198967</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>116416</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>110067</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BD5FB76-8EB2-FB49-8EC0-0F57C990A645}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId8"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19301883" y="8936567"/>
+          <a:ext cx="5842000" cy="4381500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>14816</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>29633</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>48682</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>143933</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D5A67A8D-A778-4D40-AE78-AB8F7D3F4796}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId10"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19234149" y="4500033"/>
+          <a:ext cx="5842000" cy="4381500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>91017</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>124883</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{303FF2FF-258F-3948-A133-74477E33E12F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19310350" y="0"/>
+          <a:ext cx="5842000" cy="4381500"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -565,6 +906,996 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4965700" y="13970000"/>
+          <a:ext cx="5842000" cy="4381500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2355BC48-0B74-264C-B6DA-E106DBF828DB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId6"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17373600" y="203200"/>
+          <a:ext cx="5842000" cy="4381500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>63500</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A773044D-D7FD-A742-BE6D-37360B237A84}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId8"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17360900" y="4889500"/>
+          <a:ext cx="5842000" cy="4381500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>63500</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{342E6B69-8436-0446-990F-57AB7E310E03}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId10"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17360900" y="9537700"/>
+          <a:ext cx="5842000" cy="4381500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>63500</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{989BD1EA-1A6B-7A4E-B1ED-7A9BB69C63CF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId12"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17360900" y="14173200"/>
+          <a:ext cx="5842000" cy="4381500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>736600</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>800100</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F50A9425-E61B-8F29-250D-6EE91D08F00D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17995900" y="0"/>
+          <a:ext cx="5842000" cy="4381500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>774700</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E62AA6F-ED1F-E066-4603-88F2F4760F64}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4826000" y="63500"/>
+          <a:ext cx="5842000" cy="4381500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>63500</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45C33319-77EC-A514-FCB5-A41820778E13}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4876800" y="4597400"/>
+          <a:ext cx="5842000" cy="4381500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>61468</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>49276</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0FA49FEE-8211-D1F0-48C7-22FD561143F0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4876800" y="9283700"/>
+          <a:ext cx="5839968" cy="4379976"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>101600</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79398C92-D048-46BE-5138-6467063E9602}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4914900" y="13754100"/>
+          <a:ext cx="5842000" cy="4381500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>736600</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>800100</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0590094A-B958-F82C-CC5B-91DE464CB1A7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17995900" y="4546600"/>
+          <a:ext cx="5842000" cy="4381500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>812800</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>50800</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39D10ED6-D325-4BED-BCB1-C033C7B6096D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18072100" y="9055100"/>
+          <a:ext cx="5842000" cy="4381500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>800100</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>36068</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>125476</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Picture 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{978819B0-D827-8421-4276-1D99D9B730F1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18059400" y="13627100"/>
+          <a:ext cx="5839968" cy="4379976"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>622300</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>685800</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13E2F1D2-9991-CB00-A43C-A57F2F92B187}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5829300" y="0"/>
+          <a:ext cx="5842000" cy="4381500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>596900</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE6CD778-CCC3-3654-C0C6-25FA5C789152}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5740400" y="4495800"/>
+          <a:ext cx="5842000" cy="4381500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>558800</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>620268</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>163576</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85C130B1-4F0D-3245-C1F5-1C8CC0CA3187}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5765800" y="8788400"/>
+          <a:ext cx="5839968" cy="4379976"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>673100</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>736600</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{158CAAB1-FDD9-E552-20D8-C6074C31A410}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5880100" y="13322300"/>
+          <a:ext cx="5842000" cy="4381500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Picture 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32BE7D5A-F541-4AF0-6970-207252923233}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18122900" y="88900"/>
+          <a:ext cx="5842000" cy="4381500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>50800</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="Picture 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D024B02-23A4-F5D8-361C-B8E115F14655}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18161000" y="4737100"/>
+          <a:ext cx="5842000" cy="4381500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="Picture 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3D02646-55AB-AA64-1A16-64CB4609A70E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18122900" y="9321800"/>
+          <a:ext cx="5842000" cy="4381500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>88900</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="Picture 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B81E8CE5-105E-BC87-560F-EE12416CCDC9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18135600" y="14071600"/>
           <a:ext cx="5842000" cy="4381500"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -894,10 +2225,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0FD9EE4-11F0-2F42-8458-F28E510A303E}">
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:S59"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="34.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -913,8 +2247,23 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="O1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>2</v>
+      </c>
+      <c r="R1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -930,8 +2279,23 @@
       <c r="E2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="O2" t="s">
+        <v>5</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -947,8 +2311,23 @@
       <c r="E3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="O3" t="s">
+        <v>6</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -964,8 +2343,23 @@
       <c r="E4">
         <v>0.345941</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="O4" t="s">
+        <v>7</v>
+      </c>
+      <c r="P4">
+        <v>148</v>
+      </c>
+      <c r="Q4">
+        <v>7.2094260322631552E-5</v>
+      </c>
+      <c r="R4">
+        <v>-4.1420993096139007</v>
+      </c>
+      <c r="S4">
+        <v>34.891500000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -981,8 +2375,23 @@
       <c r="E5">
         <v>8.4079500000000008E-3</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="O5" t="s">
+        <v>8</v>
+      </c>
+      <c r="P5">
+        <v>8</v>
+      </c>
+      <c r="Q5">
+        <v>4.0710417134200365E-6</v>
+      </c>
+      <c r="R5">
+        <v>-5.3902944476536803</v>
+      </c>
+      <c r="S5">
+        <v>1.1868300000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -998,8 +2407,23 @@
       <c r="E6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="O6" t="s">
+        <v>9</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -1015,8 +2439,23 @@
       <c r="E7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="O7" t="s">
+        <v>10</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -1032,8 +2471,23 @@
       <c r="E8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="O8" t="s">
+        <v>11</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>4.0958259437806932E-7</v>
+      </c>
+      <c r="R8">
+        <v>-6.3876585074183909</v>
+      </c>
+      <c r="S8">
+        <v>0.23675800000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -1049,8 +2503,23 @@
       <c r="E9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="O9" t="s">
+        <v>12</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -1066,8 +2535,23 @@
       <c r="E10">
         <v>9.6463900000000005E-2</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="O10" t="s">
+        <v>13</v>
+      </c>
+      <c r="P10">
+        <v>42</v>
+      </c>
+      <c r="Q10">
+        <v>2.0961158972424097E-5</v>
+      </c>
+      <c r="R10">
+        <v>-4.678584708262111</v>
+      </c>
+      <c r="S10">
+        <v>9.6828099999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -1083,8 +2567,23 @@
       <c r="E11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="O11" t="s">
+        <v>14</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -1100,8 +2599,23 @@
       <c r="E12">
         <v>0.14499899999999999</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="O12" t="s">
+        <v>15</v>
+      </c>
+      <c r="P12">
+        <v>59</v>
+      </c>
+      <c r="Q12">
+        <v>1.8964450975929933E-5</v>
+      </c>
+      <c r="R12">
+        <v>-4.7220597256780605</v>
+      </c>
+      <c r="S12">
+        <v>15.1737</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -1117,8 +2631,23 @@
       <c r="E13">
         <v>6.3165799999999994E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="O13" t="s">
+        <v>16</v>
+      </c>
+      <c r="P13">
+        <v>29</v>
+      </c>
+      <c r="Q13">
+        <v>1.7105733487953436E-5</v>
+      </c>
+      <c r="R13">
+        <v>-4.7668582986820187</v>
+      </c>
+      <c r="S13">
+        <v>6.7809999999999997</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -1134,8 +2663,23 @@
       <c r="E14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="O14" t="s">
+        <v>17</v>
+      </c>
+      <c r="P14">
+        <v>1</v>
+      </c>
+      <c r="Q14">
+        <v>2.8004066190410848E-6</v>
+      </c>
+      <c r="R14">
+        <v>-5.5527789045204416</v>
+      </c>
+      <c r="S14">
+        <v>0.16087399999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -1151,8 +2695,23 @@
       <c r="E15">
         <v>9.6979800000000005E-2</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="O15" t="s">
+        <v>18</v>
+      </c>
+      <c r="P15">
+        <v>48</v>
+      </c>
+      <c r="Q15">
+        <v>1.8412822382626888E-5</v>
+      </c>
+      <c r="R15">
+        <v>-4.7348796361970935</v>
+      </c>
+      <c r="S15">
+        <v>9.9104600000000005</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -1168,8 +2727,23 @@
       <c r="E16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="O16" t="s">
+        <v>19</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -1185,8 +2759,23 @@
       <c r="E17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="O17" t="s">
+        <v>20</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -1202,8 +2791,23 @@
       <c r="E18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="O18" t="s">
+        <v>21</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -1219,8 +2823,23 @@
       <c r="E19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="O19" t="s">
+        <v>22</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -1236,8 +2855,23 @@
       <c r="E20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="O20" t="s">
+        <v>23</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -1253,8 +2887,23 @@
       <c r="E21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="O21" t="s">
+        <v>24</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -1270,8 +2919,23 @@
       <c r="E22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="O22" t="s">
+        <v>25</v>
+      </c>
+      <c r="P22">
+        <v>9</v>
+      </c>
+      <c r="Q22">
+        <v>7.7595304277053171E-6</v>
+      </c>
+      <c r="R22">
+        <v>-5.110164559518469</v>
+      </c>
+      <c r="S22">
+        <v>2.0670799999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -1287,8 +2951,23 @@
       <c r="E23">
         <v>0.28265299999999999</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="O23" t="s">
+        <v>26</v>
+      </c>
+      <c r="P23">
+        <v>131</v>
+      </c>
+      <c r="Q23">
+        <v>5.0475840759896444E-5</v>
+      </c>
+      <c r="R23">
+        <v>-4.2969164384201308</v>
+      </c>
+      <c r="S23">
+        <v>29.6525</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -1304,8 +2983,23 @@
       <c r="E24">
         <v>0.122446</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="O24" t="s">
+        <v>27</v>
+      </c>
+      <c r="P24">
+        <v>48</v>
+      </c>
+      <c r="Q24">
+        <v>2.107123526165865E-5</v>
+      </c>
+      <c r="R24">
+        <v>-4.6763100039459076</v>
+      </c>
+      <c r="S24">
+        <v>13.194700000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -1321,8 +3015,23 @@
       <c r="E25">
         <v>9.0423400000000001E-2</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="O25" t="s">
+        <v>28</v>
+      </c>
+      <c r="P25">
+        <v>37</v>
+      </c>
+      <c r="Q25">
+        <v>6.0178747143542576E-5</v>
+      </c>
+      <c r="R25">
+        <v>-4.2205568580434276</v>
+      </c>
+      <c r="S25">
+        <v>9.3307000000000002</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -1338,8 +3047,23 @@
       <c r="E26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="O26" t="s">
+        <v>29</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -1355,8 +3079,23 @@
       <c r="E27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="O27" t="s">
+        <v>30</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>31</v>
       </c>
@@ -1372,8 +3111,23 @@
       <c r="E28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="O28" t="s">
+        <v>31</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>32</v>
       </c>
@@ -1389,19 +3143,270 @@
       <c r="E29">
         <v>0</v>
       </c>
+      <c r="O29" t="s">
+        <v>32</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>49</v>
+      </c>
+      <c r="B31">
+        <v>707745</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>50</v>
+      </c>
+      <c r="B32">
+        <v>3241685</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>51</v>
+      </c>
+      <c r="B33">
+        <v>2052868</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>52</v>
+      </c>
+      <c r="B34">
+        <v>1965099</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>53</v>
+      </c>
+      <c r="B35">
+        <v>1936584</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>54</v>
+      </c>
+      <c r="B36">
+        <v>1888924</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>55</v>
+      </c>
+      <c r="B37">
+        <v>2441510</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>56</v>
+      </c>
+      <c r="B38">
+        <v>149775</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>57</v>
+      </c>
+      <c r="B39">
+        <v>2003706</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>58</v>
+      </c>
+      <c r="B40">
+        <v>472594</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>59</v>
+      </c>
+      <c r="B41">
+        <v>3111084</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>60</v>
+      </c>
+      <c r="B42">
+        <v>1695338</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>61</v>
+      </c>
+      <c r="B43">
+        <v>357091</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>62</v>
+      </c>
+      <c r="B44">
+        <v>2606879</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>63</v>
+      </c>
+      <c r="B45">
+        <v>1188641</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>64</v>
+      </c>
+      <c r="B46">
+        <v>466727</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>65</v>
+      </c>
+      <c r="B47">
+        <v>672611</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>66</v>
+      </c>
+      <c r="B48">
+        <v>472825</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>67</v>
+      </c>
+      <c r="B49">
+        <v>799622</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>68</v>
+      </c>
+      <c r="B50">
+        <v>349786</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>69</v>
+      </c>
+      <c r="B51">
+        <v>1159864</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>70</v>
+      </c>
+      <c r="B52">
+        <v>2595301</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>71</v>
+      </c>
+      <c r="B53">
+        <v>2277987</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>72</v>
+      </c>
+      <c r="B54">
+        <v>614835</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>73</v>
+      </c>
+      <c r="B55">
+        <v>408688</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>74</v>
+      </c>
+      <c r="B56">
+        <v>820622</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>75</v>
+      </c>
+      <c r="B57">
+        <v>748532</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>76</v>
+      </c>
+      <c r="B58">
+        <v>222755</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>77</v>
+      </c>
+      <c r="B59">
+        <v>37429678</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06063CCF-1931-334B-A152-08BD2BA1EBAF}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:T25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="20" max="20" width="11.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1417,8 +3422,23 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="P1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R1" t="s">
+        <v>2</v>
+      </c>
+      <c r="S1" t="s">
+        <v>3</v>
+      </c>
+      <c r="T1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -1434,8 +3454,23 @@
       <c r="E2">
         <v>3.1021300000000002E-2</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="P2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q2">
+        <v>4263</v>
+      </c>
+      <c r="R2">
+        <v>8.0862763769005259E-4</v>
+      </c>
+      <c r="S2">
+        <v>-3.0922514192091719</v>
+      </c>
+      <c r="T2">
+        <v>0.59796700000000003</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>34</v>
       </c>
@@ -1451,8 +3486,23 @@
       <c r="E3">
         <v>5.1995699999999999E-2</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="P3" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q3">
+        <v>32296</v>
+      </c>
+      <c r="R3">
+        <v>5.2327619896939091E-3</v>
+      </c>
+      <c r="S3">
+        <v>-2.281269018540161</v>
+      </c>
+      <c r="T3">
+        <v>1.09273</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>35</v>
       </c>
@@ -1468,8 +3518,23 @@
       <c r="E4">
         <v>1.06845E-2</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="P4" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q4">
+        <v>2679</v>
+      </c>
+      <c r="R4">
+        <v>1.1727850822087758E-3</v>
+      </c>
+      <c r="S4">
+        <v>-2.9307815668806545</v>
+      </c>
+      <c r="T4">
+        <v>1.0805899999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>36</v>
       </c>
@@ -1485,8 +3550,23 @@
       <c r="E5">
         <v>6.6777999999999998E-4</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="P5" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q5">
+        <v>1598</v>
+      </c>
+      <c r="R5">
+        <v>1.466180276498846E-4</v>
+      </c>
+      <c r="S5">
+        <v>-3.8338126270515462</v>
+      </c>
+      <c r="T5">
+        <v>1.85764</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>37</v>
       </c>
@@ -1502,8 +3582,23 @@
       <c r="E6">
         <v>4.6441000000000003E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="P6" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q6">
+        <v>24882</v>
+      </c>
+      <c r="R6">
+        <v>3.1690126046005321E-3</v>
+      </c>
+      <c r="S6">
+        <v>-2.4990760334201219</v>
+      </c>
+      <c r="T6">
+        <v>1.8910300000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>38</v>
       </c>
@@ -1519,8 +3614,23 @@
       <c r="E7">
         <v>1.17772E-2</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="P7" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q7">
+        <v>316</v>
+      </c>
+      <c r="R7">
+        <v>8.094428164511568E-5</v>
+      </c>
+      <c r="S7">
+        <v>-4.0918138268079778</v>
+      </c>
+      <c r="T7">
+        <v>0.39459699999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>39</v>
       </c>
@@ -1536,8 +3646,23 @@
       <c r="E8">
         <v>1.3173499999999999E-2</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="P8" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q8">
+        <v>942</v>
+      </c>
+      <c r="R8">
+        <v>3.2954046945873504E-4</v>
+      </c>
+      <c r="S8">
+        <v>-3.4820912439428877</v>
+      </c>
+      <c r="T8">
+        <v>0.25193500000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -1553,9 +3678,1685 @@
       <c r="E9">
         <v>3.6394000000000003E-2</v>
       </c>
+      <c r="P9" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q9">
+        <v>12043</v>
+      </c>
+      <c r="R9">
+        <v>3.2301177975118732E-3</v>
+      </c>
+      <c r="S9">
+        <v>-2.4907816393170288</v>
+      </c>
+      <c r="T9">
+        <v>0.48869300000000004</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11">
+        <v>5271895</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12">
+        <v>6171884</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13">
+        <v>2284306</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14">
+        <v>10899069</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15">
+        <v>7851657</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16">
+        <v>3903920</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17">
+        <v>2858526</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18">
+        <v>3728347</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P21" s="2"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P24" s="2"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C309B482-4CA7-9246-8C09-0E0939E021DF}">
+  <dimension ref="A1:V59"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>0</v>
+      </c>
+      <c r="R1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S1" t="s">
+        <v>2</v>
+      </c>
+      <c r="T1" t="s">
+        <v>3</v>
+      </c>
+      <c r="U1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2">
+        <v>38</v>
+      </c>
+      <c r="C2">
+        <v>5.3691654480074036E-5</v>
+      </c>
+      <c r="D2">
+        <v>-4.2700932132746861</v>
+      </c>
+      <c r="E2">
+        <v>2.8471699999999998E-4</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>5</v>
+      </c>
+      <c r="R2">
+        <v>91</v>
+      </c>
+      <c r="S2">
+        <v>1.2857738309701941E-4</v>
+      </c>
+      <c r="T2">
+        <v>-3.8908354175704023</v>
+      </c>
+      <c r="U2">
+        <v>8.0744900000000008E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
+        <v>253</v>
+      </c>
+      <c r="C3">
+        <v>7.8045831103268823E-5</v>
+      </c>
+      <c r="D3">
+        <v>-4.1076502902594845</v>
+      </c>
+      <c r="E3">
+        <v>2.0042900000000002E-3</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>6</v>
+      </c>
+      <c r="R3">
+        <v>515</v>
+      </c>
+      <c r="S3">
+        <v>1.5886799611930215E-4</v>
+      </c>
+      <c r="T3">
+        <v>-3.7989635823941117</v>
+      </c>
+      <c r="U3">
+        <v>0.30632900000000002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4">
+        <v>170</v>
+      </c>
+      <c r="C4">
+        <v>8.2810974694914625E-5</v>
+      </c>
+      <c r="D4">
+        <v>-4.0819121036305841</v>
+      </c>
+      <c r="E4">
+        <v>3.5254700000000002E-3</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>7</v>
+      </c>
+      <c r="R4">
+        <v>114</v>
+      </c>
+      <c r="S4">
+        <v>5.5532065383648633E-5</v>
+      </c>
+      <c r="T4">
+        <v>-4.2554561736723855</v>
+      </c>
+      <c r="U4">
+        <v>0.171571</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>170</v>
+      </c>
+      <c r="C5">
+        <v>8.6509636410175774E-5</v>
+      </c>
+      <c r="D5">
+        <v>-4.0629355132673499</v>
+      </c>
+      <c r="E5">
+        <v>2.1482599999999999E-3</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>8</v>
+      </c>
+      <c r="R5">
+        <v>276</v>
+      </c>
+      <c r="S5">
+        <v>1.4045093911299125E-4</v>
+      </c>
+      <c r="T5">
+        <v>-3.8524753525804063</v>
+      </c>
+      <c r="U5">
+        <v>0.18976799999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>56</v>
+      </c>
+      <c r="C6">
+        <v>2.8916896969096101E-5</v>
+      </c>
+      <c r="D6">
+        <v>-4.5388483123976391</v>
+      </c>
+      <c r="E6">
+        <v>5.1435900000000004E-4</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>9</v>
+      </c>
+      <c r="R6">
+        <v>124</v>
+      </c>
+      <c r="S6">
+        <v>6.4030271860141368E-5</v>
+      </c>
+      <c r="T6">
+        <v>-4.1936146542416051</v>
+      </c>
+      <c r="U6">
+        <v>8.8056200000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>82</v>
+      </c>
+      <c r="C7">
+        <v>4.341095777278493E-5</v>
+      </c>
+      <c r="D7">
+        <v>-4.3624006322482209</v>
+      </c>
+      <c r="E7">
+        <v>6.0615099999999998E-4</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>10</v>
+      </c>
+      <c r="R7">
+        <v>173</v>
+      </c>
+      <c r="S7">
+        <v>9.1586532862095038E-5</v>
+      </c>
+      <c r="T7">
+        <v>-4.0381683815031417</v>
+      </c>
+      <c r="U7">
+        <v>0.110859</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8">
+        <v>272</v>
+      </c>
+      <c r="C8">
+        <v>1.1140646567083486E-4</v>
+      </c>
+      <c r="D8">
+        <v>-3.9530896033841927</v>
+      </c>
+      <c r="E8">
+        <v>2.34344E-3</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>11</v>
+      </c>
+      <c r="R8">
+        <v>554</v>
+      </c>
+      <c r="S8">
+        <v>2.2690875728545039E-4</v>
+      </c>
+      <c r="T8">
+        <v>-3.6441487426899615</v>
+      </c>
+      <c r="U8">
+        <v>0.36256299999999997</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>4.6736771824403273E-5</v>
+      </c>
+      <c r="D9">
+        <v>-4.330341288248146</v>
+      </c>
+      <c r="E9">
+        <v>6.44156E-5</v>
+      </c>
+      <c r="F9" s="1"/>
+      <c r="Q9" t="s">
+        <v>12</v>
+      </c>
+      <c r="R9">
+        <v>10</v>
+      </c>
+      <c r="S9">
+        <v>6.6766816892004674E-5</v>
+      </c>
+      <c r="T9">
+        <v>-4.1754393282624029</v>
+      </c>
+      <c r="U9">
+        <v>8.8249399999999999E-3</v>
+      </c>
+      <c r="V9" s="1"/>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10">
+        <v>255</v>
+      </c>
+      <c r="C10">
+        <v>1.2726417947543203E-4</v>
+      </c>
+      <c r="D10">
+        <v>-3.8952938182260568</v>
+      </c>
+      <c r="E10">
+        <v>2.9753599999999998E-3</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>13</v>
+      </c>
+      <c r="R10">
+        <v>466</v>
+      </c>
+      <c r="S10">
+        <v>2.3256904955118167E-4</v>
+      </c>
+      <c r="T10">
+        <v>-3.6334480819700117</v>
+      </c>
+      <c r="U10">
+        <v>0.41196999999999995</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11">
+        <v>34</v>
+      </c>
+      <c r="C11">
+        <v>7.1943359416327753E-5</v>
+      </c>
+      <c r="D11">
+        <v>-4.143009286535448</v>
+      </c>
+      <c r="E11">
+        <v>3.1595899999999999E-4</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>14</v>
+      </c>
+      <c r="R11">
+        <v>65</v>
+      </c>
+      <c r="S11">
+        <v>1.3753877535474423E-4</v>
+      </c>
+      <c r="T11">
+        <v>-3.8615748469348476</v>
+      </c>
+      <c r="U11">
+        <v>5.0244199999999996E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12">
+        <v>237</v>
+      </c>
+      <c r="C12">
+        <v>7.6179235276193117E-5</v>
+      </c>
+      <c r="D12">
+        <v>-4.1181633913101008</v>
+      </c>
+      <c r="E12">
+        <v>2.8806700000000001E-3</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>15</v>
+      </c>
+      <c r="R12">
+        <v>177</v>
+      </c>
+      <c r="S12">
+        <v>5.6893352927789802E-5</v>
+      </c>
+      <c r="T12">
+        <v>-4.2449384709583979</v>
+      </c>
+      <c r="U12">
+        <v>0.14693200000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13">
+        <v>166</v>
+      </c>
+      <c r="C13">
+        <v>9.7915577896561036E-5</v>
+      </c>
+      <c r="D13">
+        <v>-4.0091482085409202</v>
+      </c>
+      <c r="E13">
+        <v>1.55178E-3</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>16</v>
+      </c>
+      <c r="R13">
+        <v>274</v>
+      </c>
+      <c r="S13">
+        <v>1.6161968881721521E-4</v>
+      </c>
+      <c r="T13">
+        <v>-3.7915057337605869</v>
+      </c>
+      <c r="U13">
+        <v>0.20526</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14">
+        <v>7</v>
+      </c>
+      <c r="C14">
+        <v>1.9602846333287594E-5</v>
+      </c>
+      <c r="D14">
+        <v>-4.7076808645061847</v>
+      </c>
+      <c r="E14">
+        <v>1.4590100000000001E-4</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>17</v>
+      </c>
+      <c r="R14">
+        <v>3</v>
+      </c>
+      <c r="S14">
+        <v>8.4012198571232548E-6</v>
+      </c>
+      <c r="T14">
+        <v>-5.075657649800779</v>
+      </c>
+      <c r="U14">
+        <v>2.7054599999999998E-3</v>
+      </c>
+      <c r="V14" s="1"/>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15">
+        <v>265</v>
+      </c>
+      <c r="C15">
+        <v>1.0165412357075262E-4</v>
+      </c>
+      <c r="D15">
+        <v>-3.9928749996358732</v>
+      </c>
+      <c r="E15">
+        <v>2.72478E-3</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>18</v>
+      </c>
+      <c r="R15">
+        <v>573</v>
+      </c>
+      <c r="S15">
+        <v>2.1980306719260849E-4</v>
+      </c>
+      <c r="T15">
+        <v>-3.6579662516052909</v>
+      </c>
+      <c r="U15">
+        <v>0.41168000000000005</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16">
+        <v>69</v>
+      </c>
+      <c r="C16">
+        <v>5.8049486766820257E-5</v>
+      </c>
+      <c r="D16">
+        <v>-4.2362016156381248</v>
+      </c>
+      <c r="E16">
+        <v>6.8473700000000004E-4</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>19</v>
+      </c>
+      <c r="R16">
+        <v>178</v>
+      </c>
+      <c r="S16">
+        <v>1.4975084992020299E-4</v>
+      </c>
+      <c r="T16">
+        <v>-3.824630704066486</v>
+      </c>
+      <c r="U16">
+        <v>0.11543300000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17">
+        <v>28</v>
+      </c>
+      <c r="C17">
+        <v>5.9992243859900972E-5</v>
+      </c>
+      <c r="D17">
+        <v>-4.2219048940594002</v>
+      </c>
+      <c r="E17">
+        <v>2.7151200000000001E-4</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>20</v>
+      </c>
+      <c r="R17">
+        <v>70</v>
+      </c>
+      <c r="S17">
+        <v>1.4998060964975242E-4</v>
+      </c>
+      <c r="T17">
+        <v>-3.8239648853873631</v>
+      </c>
+      <c r="U17">
+        <v>5.8650399999999998E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18">
+        <v>29</v>
+      </c>
+      <c r="C18">
+        <v>4.311556010829439E-5</v>
+      </c>
+      <c r="D18">
+        <v>-4.3653659676669889</v>
+      </c>
+      <c r="E18">
+        <v>3.8198399999999998E-4</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>21</v>
+      </c>
+      <c r="R18">
+        <v>53</v>
+      </c>
+      <c r="S18">
+        <v>7.8797402956538035E-5</v>
+      </c>
+      <c r="T18">
+        <v>-4.1034880959651554</v>
+      </c>
+      <c r="U18">
+        <v>4.6024999999999996E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19">
+        <v>17</v>
+      </c>
+      <c r="C19">
+        <v>3.5954105641622168E-5</v>
+      </c>
+      <c r="D19">
+        <v>-4.4442515098515409</v>
+      </c>
+      <c r="E19">
+        <v>1.58462E-4</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>22</v>
+      </c>
+      <c r="R19">
+        <v>49</v>
+      </c>
+      <c r="S19">
+        <v>1.0363242214349918E-4</v>
+      </c>
+      <c r="T19">
+        <v>-3.9845043512013016</v>
+      </c>
+      <c r="U19">
+        <v>3.9293500000000002E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20">
+        <v>63</v>
+      </c>
+      <c r="C20">
+        <v>7.8787226964740841E-5</v>
+      </c>
+      <c r="D20">
+        <v>-4.1035441849009073</v>
+      </c>
+      <c r="E20">
+        <v>5.4205699999999998E-4</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>23</v>
+      </c>
+      <c r="R20">
+        <v>122</v>
+      </c>
+      <c r="S20">
+        <v>1.5257209031267275E-4</v>
+      </c>
+      <c r="T20">
+        <v>-3.8165249036797411</v>
+      </c>
+      <c r="U20">
+        <v>8.8152700000000001E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21">
+        <v>100</v>
+      </c>
+      <c r="C21">
+        <v>2.8588908647001312E-4</v>
+      </c>
+      <c r="D21">
+        <v>-3.5438024230831324</v>
+      </c>
+      <c r="E21">
+        <v>1.2071499999999999E-3</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>24</v>
+      </c>
+      <c r="R21">
+        <v>194</v>
+      </c>
+      <c r="S21">
+        <v>5.546248277518254E-4</v>
+      </c>
+      <c r="T21">
+        <v>-3.2560006931529064</v>
+      </c>
+      <c r="U21">
+        <v>0.18715899999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22">
+        <v>61</v>
+      </c>
+      <c r="C22">
+        <v>5.2592372898891596E-5</v>
+      </c>
+      <c r="D22">
+        <v>-4.2790772339470262</v>
+      </c>
+      <c r="E22">
+        <v>1.5140900000000001E-3</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>25</v>
+      </c>
+      <c r="R22">
+        <v>23</v>
+      </c>
+      <c r="S22">
+        <v>1.98299110930247E-5</v>
+      </c>
+      <c r="T22">
+        <v>-4.7026792329402012</v>
+      </c>
+      <c r="U22">
+        <v>7.9263399999999998E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23">
+        <v>185</v>
+      </c>
+      <c r="C23">
+        <v>7.12826758822965E-5</v>
+      </c>
+      <c r="D23">
+        <v>-4.1470160056728806</v>
+      </c>
+      <c r="E23">
+        <v>2.7309000000000001E-3</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>26</v>
+      </c>
+      <c r="R23">
+        <v>90</v>
+      </c>
+      <c r="S23">
+        <v>3.4678058537333437E-5</v>
+      </c>
+      <c r="T23">
+        <v>-4.4599452246365701</v>
+      </c>
+      <c r="U23">
+        <v>0.114466</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24">
+        <v>219</v>
+      </c>
+      <c r="C24">
+        <v>9.6137510881317588E-5</v>
+      </c>
+      <c r="D24">
+        <v>-4.0171071264813767</v>
+      </c>
+      <c r="E24">
+        <v>3.2517000000000002E-3</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>27</v>
+      </c>
+      <c r="R24">
+        <v>117</v>
+      </c>
+      <c r="S24">
+        <v>5.1361135950292953E-5</v>
+      </c>
+      <c r="T24">
+        <v>-4.289365379575333</v>
+      </c>
+      <c r="U24">
+        <v>0.11060200000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25">
+        <v>101</v>
+      </c>
+      <c r="C25">
+        <v>1.6427171517561622E-4</v>
+      </c>
+      <c r="D25">
+        <v>-3.78443720832778</v>
+      </c>
+      <c r="E25">
+        <v>1.5469399999999999E-3</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>28</v>
+      </c>
+      <c r="R25">
+        <v>148</v>
+      </c>
+      <c r="S25">
+        <v>2.407149885741703E-4</v>
+      </c>
+      <c r="T25">
+        <v>-3.6184968667154651</v>
+      </c>
+      <c r="U25">
+        <v>0.18790099999999998</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26">
+        <v>22</v>
+      </c>
+      <c r="C26">
+        <v>5.3830795129781154E-5</v>
+      </c>
+      <c r="D26">
+        <v>-4.268969205212624</v>
+      </c>
+      <c r="E26">
+        <v>1.96145E-4</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>29</v>
+      </c>
+      <c r="R26">
+        <v>38</v>
+      </c>
+      <c r="S26">
+        <v>9.2980464315076534E-5</v>
+      </c>
+      <c r="T26">
+        <v>-4.0316082894180196</v>
+      </c>
+      <c r="U26">
+        <v>3.2723099999999998E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27">
+        <v>51</v>
+      </c>
+      <c r="C27">
+        <v>6.2147980434353454E-5</v>
+      </c>
+      <c r="D27">
+        <v>-4.2065729796605815</v>
+      </c>
+      <c r="E27">
+        <v>4.8086199999999998E-4</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>30</v>
+      </c>
+      <c r="R27">
+        <v>124</v>
+      </c>
+      <c r="S27">
+        <v>1.5110489360509467E-4</v>
+      </c>
+      <c r="T27">
+        <v>-3.8207214705962826</v>
+      </c>
+      <c r="U27">
+        <v>9.9618699999999991E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28">
+        <v>35</v>
+      </c>
+      <c r="C28">
+        <v>4.6758188026697587E-5</v>
+      </c>
+      <c r="D28">
+        <v>-4.330142326963875</v>
+      </c>
+      <c r="E28">
+        <v>2.8246199999999998E-4</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>31</v>
+      </c>
+      <c r="R28">
+        <v>101</v>
+      </c>
+      <c r="S28">
+        <v>1.349307711627559E-4</v>
+      </c>
+      <c r="T28">
+        <v>-3.8698889975315081</v>
+      </c>
+      <c r="U28">
+        <v>7.3369400000000001E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29">
+        <v>18</v>
+      </c>
+      <c r="C29">
+        <v>8.080626697492761E-5</v>
+      </c>
+      <c r="D29">
+        <v>-4.0925549559694163</v>
+      </c>
+      <c r="E29">
+        <v>2.01621E-4</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>32</v>
+      </c>
+      <c r="R29">
+        <v>29</v>
+      </c>
+      <c r="S29">
+        <v>1.3018787457071672E-4</v>
+      </c>
+      <c r="T29">
+        <v>-3.8854294631737663</v>
+      </c>
+      <c r="U29">
+        <v>2.71512E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>49</v>
+      </c>
+      <c r="B31">
+        <v>707745</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>50</v>
+      </c>
+      <c r="B32">
+        <v>3241685</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>51</v>
+      </c>
+      <c r="B33">
+        <v>2052868</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>52</v>
+      </c>
+      <c r="B34">
+        <v>1965099</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>53</v>
+      </c>
+      <c r="B35">
+        <v>1936584</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>54</v>
+      </c>
+      <c r="B36">
+        <v>1888924</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>55</v>
+      </c>
+      <c r="B37">
+        <v>2441510</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>56</v>
+      </c>
+      <c r="B38">
+        <v>149775</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>57</v>
+      </c>
+      <c r="B39">
+        <v>2003706</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>58</v>
+      </c>
+      <c r="B40">
+        <v>472594</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>59</v>
+      </c>
+      <c r="B41">
+        <v>3111084</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>60</v>
+      </c>
+      <c r="B42">
+        <v>1695338</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>61</v>
+      </c>
+      <c r="B43">
+        <v>357091</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>62</v>
+      </c>
+      <c r="B44">
+        <v>2606879</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>63</v>
+      </c>
+      <c r="B45">
+        <v>1188641</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>64</v>
+      </c>
+      <c r="B46">
+        <v>466727</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>65</v>
+      </c>
+      <c r="B47">
+        <v>672611</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>66</v>
+      </c>
+      <c r="B48">
+        <v>472825</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>67</v>
+      </c>
+      <c r="B49">
+        <v>799622</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>68</v>
+      </c>
+      <c r="B50">
+        <v>349786</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>69</v>
+      </c>
+      <c r="B51">
+        <v>1159864</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>70</v>
+      </c>
+      <c r="B52">
+        <v>2595301</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>71</v>
+      </c>
+      <c r="B53">
+        <v>2277987</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>72</v>
+      </c>
+      <c r="B54">
+        <v>614835</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>73</v>
+      </c>
+      <c r="B55">
+        <v>408688</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>74</v>
+      </c>
+      <c r="B56">
+        <v>820622</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>75</v>
+      </c>
+      <c r="B57">
+        <v>748532</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>76</v>
+      </c>
+      <c r="B58">
+        <v>222755</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>77</v>
+      </c>
+      <c r="B59">
+        <v>37429678</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A81953DE-CC63-864B-9AA1-3FFAF6517F99}">
+  <dimension ref="A1:S18"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="O1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>2</v>
+      </c>
+      <c r="R1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2">
+        <v>3803</v>
+      </c>
+      <c r="C2">
+        <f>B2/$B11</f>
+        <v>7.2137248560527102E-4</v>
+      </c>
+      <c r="D2">
+        <f>LOG10(C2)</f>
+        <v>-3.1418404264447215</v>
+      </c>
+      <c r="E2">
+        <v>0.46759299999999998</v>
+      </c>
+      <c r="O2" t="s">
+        <v>78</v>
+      </c>
+      <c r="P2">
+        <v>29082</v>
+      </c>
+      <c r="Q2">
+        <f t="shared" ref="Q2:Q9" si="0">P2/$B11</f>
+        <v>5.5164224628904785E-3</v>
+      </c>
+      <c r="R2">
+        <f>LOG10(Q2)</f>
+        <v>-2.2583424817499012</v>
+      </c>
+      <c r="S2">
+        <v>0.84194400000000003</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3">
+        <v>5085</v>
+      </c>
+      <c r="C3">
+        <f t="shared" ref="C3:C9" si="1">B3/$B12</f>
+        <v>8.2389753274688901E-4</v>
+      </c>
+      <c r="D3">
+        <f t="shared" ref="D3:D9" si="2">LOG10(C3)</f>
+        <v>-3.0841267976836555</v>
+      </c>
+      <c r="E3">
+        <v>0.75562700000000005</v>
+      </c>
+      <c r="O3" t="s">
+        <v>79</v>
+      </c>
+      <c r="P3">
+        <v>37285</v>
+      </c>
+      <c r="Q3">
+        <f t="shared" si="0"/>
+        <v>6.0411051147429215E-3</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R9" si="3">LOG10(Q3)</f>
+        <v>-2.2188836075157488</v>
+      </c>
+      <c r="S3">
+        <v>0.98852200000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4">
+        <v>1663</v>
+      </c>
+      <c r="C4">
+        <f t="shared" si="1"/>
+        <v>7.2801104580559692E-4</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="2"/>
+        <v>-3.1378620312693442</v>
+      </c>
+      <c r="E4">
+        <v>0.19015499999999999</v>
+      </c>
+      <c r="O4" t="s">
+        <v>80</v>
+      </c>
+      <c r="P4">
+        <v>32966</v>
+      </c>
+      <c r="Q4">
+        <f t="shared" si="0"/>
+        <v>1.4431516618176373E-2</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="3"/>
+        <v>-1.8406880261972558</v>
+      </c>
+      <c r="S4">
+        <v>0.38981100000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5">
+        <v>463</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="1"/>
+        <v>4.2480692616956552E-5</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="2"/>
+        <v>-4.3718084110115658</v>
+      </c>
+      <c r="E5">
+        <v>0.28590899999999997</v>
+      </c>
+      <c r="O5" t="s">
+        <v>81</v>
+      </c>
+      <c r="P5">
+        <v>89317</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" si="0"/>
+        <v>8.1949201349216152E-3</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="3"/>
+        <v>-2.086455274568388</v>
+      </c>
+      <c r="S5">
+        <v>2.4271500000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6">
+        <v>42006</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="1"/>
+        <v>5.3499535193654024E-3</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="2"/>
+        <v>-2.2716499911321941</v>
+      </c>
+      <c r="E6">
+        <v>1.44343</v>
+      </c>
+      <c r="O6" t="s">
+        <v>82</v>
+      </c>
+      <c r="P6">
+        <v>94997</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="0"/>
+        <v>1.2098974776916516E-2</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="3"/>
+        <v>-1.9172514286580724</v>
+      </c>
+      <c r="S6">
+        <v>2.1863000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B7">
+        <v>306</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="1"/>
+        <v>7.8382753744953791E-5</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="2"/>
+        <v>-4.1057794829448016</v>
+      </c>
+      <c r="E7">
+        <v>4.8182900000000001E-2</v>
+      </c>
+      <c r="O7" t="s">
+        <v>83</v>
+      </c>
+      <c r="P7">
+        <v>43147</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="0"/>
+        <v>1.1052224430828501E-2</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="3"/>
+        <v>-1.9565503047109409</v>
+      </c>
+      <c r="S7">
+        <v>0.263492</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8">
+        <v>685</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="1"/>
+        <v>2.3963399318389968E-4</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="2"/>
+        <v>-3.6204515752433397</v>
+      </c>
+      <c r="E8">
+        <v>0.109474</v>
+      </c>
+      <c r="O8" t="s">
+        <v>84</v>
+      </c>
+      <c r="P8">
+        <v>24749</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="0"/>
+        <v>8.6579586822019463E-3</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="3"/>
+        <v>-2.0625844910724713</v>
+      </c>
+      <c r="S8">
+        <v>0.36288500000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9">
+        <v>3290</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="1"/>
+        <v>8.8242859369044781E-4</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="2"/>
+        <v>-3.0543204277201976</v>
+      </c>
+      <c r="E9">
+        <v>0.61671500000000001</v>
+      </c>
+      <c r="O9" t="s">
+        <v>85</v>
+      </c>
+      <c r="P9">
+        <v>16730</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="0"/>
+        <v>4.4872432742982344E-3</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="3"/>
+        <v>-2.3480203847077772</v>
+      </c>
+      <c r="S9">
+        <v>0.93859900000000007</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11">
+        <v>5271895</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12">
+        <v>6171884</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13">
+        <v>2284306</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14">
+        <v>10899069</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15">
+        <v>7851657</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16">
+        <v>3903920</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17">
+        <v>2858526</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18">
+        <v>3728347</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>